--- a/output/2026-10-03_23_Malesia_Pulau_Pinang_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-03_23_Malesia_Pulau_Pinang_ATEX_Equipment_Services.xlsx
@@ -479,11 +479,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rappresentante/distributore per Deeter Electronics a Penang; prodotti per aree pericolose con certificazione ATEX &amp; IECEx (sensori di livello, interruttori a galleggiante, rilevatori di perdite). Sede Penang confermata tramite pagina ufficiale Deeter Electronics. Sito web proprio e contatti diretti (telefono/email) non reperiti.</t>
+          <t>Rappresentante/distributore per Deeter Electronics a Penang; prodotti per aree pericolose con certificazione ATEX &amp; IECEx (sensori di livello, interruttori a galleggiante, rilevatori di perdite). Sede Penang confermata tramite pagina ufficiale Deeter Electronics. Sito web proprio e contatti diretti (telefono/email) non reperiti. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -525,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Progetta, produce e installa Air Pollution Control Systems (fume scrubber, dust collector, welding fume collector, oil mist collector) - settore affine aspirazione industriale/dust collection. Certificazione ATEX specifica non confermata dalle fonti pubbliche consultate. Sede Penang e contatti verificati via sito ufficiale.</t>
+          <t>Progetta, produce e installa Air Pollution Control Systems (fume scrubber, dust collector, welding fume collector, oil mist collector) - settore affine aspirazione industriale/dust collection. Certificazione ATEX specifica non confermata dalle fonti pubbliche consultate. Sede Penang e contatti verificati via sito ufficiale. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,10 +558,9 @@
           <t>+604-588 0072</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>System integrator in plant automation &amp; bulk solids handling (conveying, filling, discharging, weighing, blending polveri/solidi sfusi) - settore affine aspirazione industriale/gestione polveri. Fondata nel 2004, sede Penang confermata (investpenang.gov.my). Email aziendale offuscata/non decodificabile con certezza dal sito; contatto diretto originale (bhcheng@bafe.com.my, Cheng Boon Hung, Direttore) non confermato come email generica, lasciato vuoto per non rischiare dati inventati.</t>
+          <t>System integrator in plant automation &amp; bulk solids handling (conveying, filling, discharging, weighing, blending polveri/solidi sfusi) - settore affine aspirazione industriale/gestione polveri. Fondata nel 2004, sede Penang confermata (investpenang.gov.my). Email aziendale offuscata/non decodificabile con certezza dal sito; contatto diretto originale (bhcheng@bafe.com.my, Cheng Boon Hung, Direttore) non confermato come email generica, lasciato vuoto per non rischiare dati inventati. [DUPLICATO — vedi anche: 2026-10-03_22_Malesia_Pulau_Pinang_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -605,7 +602,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore/stockist di prodotti per atmosfere esplosive (Crouse-Hinds/CEAG, Thuba, WINNEX). Ufficio vendite a Penang confermato tramite directory Malaysian-German Chamber of Commerce and Industry; telefono/email riportati sono quelli generali della sede HQ, recapito specifico dell'ufficio di Penang non reperito pubblicamente.</t>
+          <t>Distributore/stockist di prodotti per atmosfere esplosive (Crouse-Hinds/CEAG, Thuba, WINNEX). Ufficio vendite a Penang confermato tramite directory Malaysian-German Chamber of Commerce and Industry; telefono/email riportati sono quelli generali della sede HQ, recapito specifico dell'ufficio di Penang non reperito pubblicamente. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
